--- a/data/batches/B08_Findings_structural/Test_Validation_Report/Test_Validation_Report_B08.xlsx
+++ b/data/batches/B08_Findings_structural/Test_Validation_Report/Test_Validation_Report_B08.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=42</t>
+          <t>Complete Row @ CSV Row 182; count=1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=44</t>
+          <t>Complete Row @ CSV Row 182; count=2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=49</t>
+          <t>Complete Row @ CSV Row 963; count=1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=53</t>
+          <t>Complete Row @ CSV Row 963; count=2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=84</t>
+          <t>Complete Row @ CSV Row 684; count=1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=85</t>
+          <t>Complete Row @ CSV Row 684; count=2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1710,17 +1710,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=70</t>
+          <t>Complete Row @ CSV Row 33; count=1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=71</t>
+          <t>Complete Row @ CSV Row 33; count=2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1793,17 +1793,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=56</t>
+          <t>Complete Row @ CSV Row 891; count=1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=57</t>
+          <t>Complete Row @ CSV Row 891; count=2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=77</t>
+          <t>Complete Row @ CSV Row 391; count=1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=78</t>
+          <t>Complete Row @ CSV Row 391; count=2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=56</t>
+          <t>Complete Row @ CSV Row 631; count=1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=57</t>
+          <t>Complete Row @ CSV Row 631; count=2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=80</t>
+          <t>Complete Row @ CSV Row 794; count=1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=81</t>
+          <t>Complete Row @ CSV Row 794; count=2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=54</t>
+          <t>Complete Row @ CSV Row 569; count=1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=56</t>
+          <t>Complete Row @ CSV Row 569; count=2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=96</t>
+          <t>Complete Row @ CSV Row 132; count=1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=97</t>
+          <t>Complete Row @ CSV Row 132; count=2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=72</t>
+          <t>Complete Row @ CSV Row 965; count=1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=73</t>
+          <t>Complete Row @ CSV Row 965; count=2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=87</t>
+          <t>Complete Row @ CSV Row 875; count=1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=88</t>
+          <t>Complete Row @ CSV Row 875; count=2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=54</t>
+          <t>Complete Row @ CSV Row 582; count=1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=56</t>
+          <t>Complete Row @ CSV Row 582; count=2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 1928; count=1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 1928; count=2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=765</t>
+          <t>Complete Row @ CSV Row 4543; count=1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=770</t>
+          <t>Complete Row @ CSV Row 4543; count=2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9454; count=1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9454; count=2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5134; count=1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5134; count=2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=765</t>
+          <t>Complete Row @ CSV Row 4130; count=1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=770</t>
+          <t>Complete Row @ CSV Row 4130; count=2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 2430; count=1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 2430; count=2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5870; count=1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5870; count=2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=639</t>
+          <t>Complete Row @ CSV Row 10318; count=1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=641</t>
+          <t>Complete Row @ CSV Row 10318; count=2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5525; count=1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5525; count=2</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=411</t>
+          <t>Complete Row @ CSV Row 6795; count=1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=413</t>
+          <t>Complete Row @ CSV Row 6795; count=2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9484; count=1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9484; count=2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 8737; count=1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 8737; count=2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5561; count=1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5561; count=2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=102</t>
+          <t>Complete Row @ CSV Row 6912; count=1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=103</t>
+          <t>Complete Row @ CSV Row 6912; count=2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3702,17 +3702,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5827; count=1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5827; count=2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3785,17 +3785,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=807</t>
+          <t>Complete Row @ CSV Row 8459; count=1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=810</t>
+          <t>Complete Row @ CSV Row 8459; count=2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3868,17 +3868,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1275</t>
+          <t>Complete Row @ CSV Row 2833; count=1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1278</t>
+          <t>Complete Row @ CSV Row 2833; count=2</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1329</t>
+          <t>Complete Row @ CSV Row 11315; count=1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1334</t>
+          <t>Complete Row @ CSV Row 11315; count=2</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4034,17 +4034,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1050</t>
+          <t>Complete Row @ CSV Row 797; count=1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1054</t>
+          <t>Complete Row @ CSV Row 797; count=2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4117,17 +4117,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1329</t>
+          <t>Complete Row @ CSV Row 11522; count=1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1334</t>
+          <t>Complete Row @ CSV Row 11522; count=2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4200,17 +4200,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9946; count=1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9946; count=2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1050</t>
+          <t>Complete Row @ CSV Row 849; count=1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1054</t>
+          <t>Complete Row @ CSV Row 849; count=2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=765</t>
+          <t>Complete Row @ CSV Row 4581; count=1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=770</t>
+          <t>Complete Row @ CSV Row 4581; count=2</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4449,17 +4449,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=639</t>
+          <t>Complete Row @ CSV Row 10249; count=1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=641</t>
+          <t>Complete Row @ CSV Row 10249; count=2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 8584; count=1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 8584; count=2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 1150; count=1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 1150; count=2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4698,17 +4698,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9713; count=1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9713; count=2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=765</t>
+          <t>Complete Row @ CSV Row 4630; count=1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=770</t>
+          <t>Complete Row @ CSV Row 4630; count=2</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4864,17 +4864,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=558</t>
+          <t>Complete Row @ CSV Row 12109; count=1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=560</t>
+          <t>Complete Row @ CSV Row 12109; count=2</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5788; count=1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5788; count=2</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 1626; count=1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 1626; count=2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1329</t>
+          <t>Complete Row @ CSV Row 10699; count=1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1334</t>
+          <t>Complete Row @ CSV Row 10699; count=2</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9303; count=1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9303; count=2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5279,17 +5279,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 2062; count=1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 2062; count=2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1275</t>
+          <t>Complete Row @ CSV Row 4072; count=1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1278</t>
+          <t>Complete Row @ CSV Row 4072; count=2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1050</t>
+          <t>Complete Row @ CSV Row 548; count=1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1054</t>
+          <t>Complete Row @ CSV Row 548; count=2</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=765</t>
+          <t>Complete Row @ CSV Row 4423; count=1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0006; count=770</t>
+          <t>Complete Row @ CSV Row 4423; count=2</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1404</t>
+          <t>Complete Row @ CSV Row 9283; count=1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0019; count=1412</t>
+          <t>Complete Row @ CSV Row 9283; count=2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5694,17 +5694,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1050</t>
+          <t>Complete Row @ CSV Row 955; count=1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0015; count=1054</t>
+          <t>Complete Row @ CSV Row 955; count=2</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5777,17 +5777,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=807</t>
+          <t>Complete Row @ CSV Row 7876; count=1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=810</t>
+          <t>Complete Row @ CSV Row 7876; count=2</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5860,17 +5860,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1035</t>
+          <t>Complete Row @ CSV Row 5613; count=1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1042</t>
+          <t>Complete Row @ CSV Row 5613; count=2</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5943,17 +5943,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=411</t>
+          <t>Complete Row @ CSV Row 6825; count=1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=413</t>
+          <t>Complete Row @ CSV Row 6825; count=2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=603</t>
+          <t>Complete Row @ CSV Row 5949; count=1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=605</t>
+          <t>Complete Row @ CSV Row 5949; count=2</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6109,17 +6109,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=558</t>
+          <t>Complete Row @ CSV Row 12087; count=1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=560</t>
+          <t>Complete Row @ CSV Row 12087; count=2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6192,17 +6192,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1329</t>
+          <t>Complete Row @ CSV Row 11066; count=1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1334</t>
+          <t>Complete Row @ CSV Row 11066; count=2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6275,17 +6275,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1329</t>
+          <t>Complete Row @ CSV Row 11143; count=1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1334</t>
+          <t>Complete Row @ CSV Row 11143; count=2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6358,17 +6358,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1374</t>
+          <t>Complete Row @ CSV Row 2370; count=1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0009; count=1380</t>
+          <t>Complete Row @ CSV Row 2370; count=2</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=807</t>
+          <t>Complete Row @ CSV Row 8531; count=1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0017; count=810</t>
+          <t>Complete Row @ CSV Row 8531; count=2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=603</t>
+          <t>Complete Row @ CSV Row 6215; count=1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=605</t>
+          <t>Complete Row @ CSV Row 6215; count=2</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1275</t>
+          <t>Complete Row @ CSV Row 3452; count=1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=1278</t>
+          <t>Complete Row @ CSV Row 3452; count=2</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6690,17 +6690,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=1</t>
+          <t>Complete Row @ CSV Row 2; count=1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=2</t>
+          <t>Complete Row @ CSV Row 2; count=0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6768,22 +6768,22 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Duplicate row injection verified successfully</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=49</t>
+          <t>Complete Row @ CSV Row 553; count=1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=54</t>
+          <t>Complete Row @ CSV Row 553; count=2</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=49</t>
+          <t>Complete Row @ CSV Row 956; count=1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=53</t>
+          <t>Complete Row @ CSV Row 956; count=2</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=49</t>
+          <t>Complete Row @ CSV Row 969; count=1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=53</t>
+          <t>Complete Row @ CSV Row 969; count=2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=91</t>
+          <t>Complete Row @ CSV Row 230; count=1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=96</t>
+          <t>Complete Row @ CSV Row 230; count=2</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=49</t>
+          <t>Complete Row @ CSV Row 534; count=1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=54</t>
+          <t>Complete Row @ CSV Row 534; count=2</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=42</t>
+          <t>Complete Row @ CSV Row 210; count=1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=44</t>
+          <t>Complete Row @ CSV Row 210; count=2</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7271,17 +7271,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=84</t>
+          <t>Complete Row @ CSV Row 660; count=1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=87</t>
+          <t>Complete Row @ CSV Row 660; count=2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7354,17 +7354,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=49</t>
+          <t>Complete Row @ CSV Row 989; count=1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0014; count=53</t>
+          <t>Complete Row @ CSV Row 989; count=2</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7437,17 +7437,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=56</t>
+          <t>Complete Row @ CSV Row 841; count=1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=58</t>
+          <t>Complete Row @ CSV Row 841; count=2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7520,17 +7520,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=84</t>
+          <t>Complete Row @ CSV Row 654; count=1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=87</t>
+          <t>Complete Row @ CSV Row 654; count=2</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=91</t>
+          <t>Complete Row @ CSV Row 290; count=1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=96</t>
+          <t>Complete Row @ CSV Row 290; count=2</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7686,17 +7686,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=49</t>
+          <t>Complete Row @ CSV Row 545; count=1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=54</t>
+          <t>Complete Row @ CSV Row 545; count=2</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7769,17 +7769,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=84</t>
+          <t>Complete Row @ CSV Row 611; count=1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=87</t>
+          <t>Complete Row @ CSV Row 611; count=2</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -7852,17 +7852,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=49</t>
+          <t>Complete Row @ CSV Row 501; count=1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=51</t>
+          <t>Complete Row @ CSV Row 501; count=2</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=35</t>
+          <t>Complete Row @ CSV Row 584; count=1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=36</t>
+          <t>Complete Row @ CSV Row 584; count=2</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -8018,17 +8018,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=91</t>
+          <t>Complete Row @ CSV Row 271; count=1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=96</t>
+          <t>Complete Row @ CSV Row 271; count=2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -8101,17 +8101,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=49</t>
+          <t>Complete Row @ CSV Row 541; count=1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=54</t>
+          <t>Complete Row @ CSV Row 541; count=2</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -8184,17 +8184,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=56</t>
+          <t>Complete Row @ CSV Row 834; count=1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0007; count=58</t>
+          <t>Complete Row @ CSV Row 834; count=2</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=49</t>
+          <t>Complete Row @ CSV Row 552; count=1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0005; count=54</t>
+          <t>Complete Row @ CSV Row 552; count=2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8350,17 +8350,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=49</t>
+          <t>Complete Row @ CSV Row 466; count=1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE01-0016; count=51</t>
+          <t>Complete Row @ CSV Row 466; count=2</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8433,17 +8433,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=91</t>
+          <t>Complete Row @ CSV Row 278; count=1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=96</t>
+          <t>Complete Row @ CSV Row 278; count=2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=91</t>
+          <t>Complete Row @ CSV Row 295; count=1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0008; count=96</t>
+          <t>Complete Row @ CSV Row 295; count=2</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -8599,17 +8599,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=20</t>
+          <t>Complete Row @ CSV Row 63; count=1</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=21</t>
+          <t>Complete Row @ CSV Row 63; count=2</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=20</t>
+          <t>Complete Row @ CSV Row 211; count=1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=21</t>
+          <t>Complete Row @ CSV Row 211; count=2</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=20</t>
+          <t>Complete Row @ CSV Row 236; count=1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=23</t>
+          <t>Complete Row @ CSV Row 236; count=2</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=20</t>
+          <t>Complete Row @ CSV Row 225; count=1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=23</t>
+          <t>Complete Row @ CSV Row 225; count=2</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8931,17 +8931,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=20</t>
+          <t>Complete Row @ CSV Row 235; count=1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0012; count=23</t>
+          <t>Complete Row @ CSV Row 235; count=2</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -9014,17 +9014,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=20</t>
+          <t>Complete Row @ CSV Row 8; count=1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=21</t>
+          <t>Complete Row @ CSV Row 8; count=2</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -9097,17 +9097,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=4</t>
+          <t>Complete Row @ CSV Row 15; count=1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=5</t>
+          <t>Complete Row @ CSV Row 15; count=2</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=5</t>
+          <t>Complete Row @ CSV Row 75; count=1</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=6</t>
+          <t>Complete Row @ CSV Row 75; count=2</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9263,17 +9263,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=16</t>
+          <t>Complete Row @ CSV Row 1096; count=1</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=19</t>
+          <t>Complete Row @ CSV Row 1096; count=2</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -9346,17 +9346,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=24</t>
+          <t>Complete Row @ CSV Row 13; count=1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=26</t>
+          <t>Complete Row @ CSV Row 13; count=2</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=16</t>
+          <t>Complete Row @ CSV Row 1109; count=1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=19</t>
+          <t>Complete Row @ CSV Row 1109; count=2</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=18</t>
+          <t>Complete Row @ CSV Row 14; count=1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=20</t>
+          <t>Complete Row @ CSV Row 14; count=2</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -9595,17 +9595,17 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=18</t>
+          <t>Complete Row @ CSV Row 6; count=1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=20</t>
+          <t>Complete Row @ CSV Row 6; count=2</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=36</t>
+          <t>Complete Row @ CSV Row 177; count=1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0003; count=37</t>
+          <t>Complete Row @ CSV Row 177; count=2</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -9761,17 +9761,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=16</t>
+          <t>Complete Row @ CSV Row 1102; count=1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=19</t>
+          <t>Complete Row @ CSV Row 1102; count=2</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -9844,17 +9844,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=24</t>
+          <t>Complete Row @ CSV Row 12; count=1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=26</t>
+          <t>Complete Row @ CSV Row 12; count=2</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -9927,17 +9927,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -10944,10 +10944,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
